--- a/docs/sound_presets.xlsx
+++ b/docs/sound_presets.xlsx
@@ -107,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -138,6 +138,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -503,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT84"/>
+  <dimension ref="A1:AT104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -15294,6 +15297,3486 @@
         </is>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" s="12" t="inlineStr">
+        <is>
+          <t>victory_fanfare</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>Short triumphant sting</t>
+        </is>
+      </c>
+      <c r="C85" s="12" t="inlineStr">
+        <is>
+          <t>Platformer 2D</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>Rapid 3-note arpeggio fanfare — bright square with vibrato, updown mode, punchy and short</t>
+        </is>
+      </c>
+      <c r="E85" s="12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F85" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G85" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="H85" s="12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I85" s="12" t="n">
+        <v>523</v>
+      </c>
+      <c r="J85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L85" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M85" s="12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N85" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="O85" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="P85" s="12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="Q85" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R85" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="S85" s="12" t="inlineStr">
+        <is>
+          <t>updown</t>
+        </is>
+      </c>
+      <c r="T85" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="U85" s="12" t="inlineStr">
+        <is>
+          <t>square</t>
+        </is>
+      </c>
+      <c r="V85" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="W85" s="12" t="n">
+        <v>22050</v>
+      </c>
+      <c r="X85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Z85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB85" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AC85" s="12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AD85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AF85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AI85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ85" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AK85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL85" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AM85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ85" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AR85" s="12" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="AS85" s="12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AT85" s="5" t="inlineStr">
+        <is>
+          <t>New platformer preset: short punchy victory sting, rapid arp updown, vibrato shimmer. Distinct from 'victory' (which is longer/grander).</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="12" t="inlineStr">
+        <is>
+          <t>panel_open_2d</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>UI panel slides in</t>
+        </is>
+      </c>
+      <c r="C86" s="12" t="inlineStr">
+        <is>
+          <t>Platformer 2D</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>Panel swoops open — sine rising slide from low to mid, soft attack</t>
+        </is>
+      </c>
+      <c r="E86" s="12" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F86" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I86" s="12" t="n">
+        <v>280</v>
+      </c>
+      <c r="J86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" s="12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" s="12" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="T86" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="U86" s="12" t="inlineStr">
+        <is>
+          <t>sine</t>
+        </is>
+      </c>
+      <c r="V86" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="W86" s="12" t="n">
+        <v>22050</v>
+      </c>
+      <c r="X86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Z86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB86" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AC86" s="12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AD86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AF86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AI86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ86" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AK86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL86" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AM86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ86" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AR86" s="12" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="AS86" s="12" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AT86" s="5" t="inlineStr">
+        <is>
+          <t>New platformer preset: soft sine whoosh for panel sliding open. Slide 0.35 gives clear upward sweep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="12" t="inlineStr">
+        <is>
+          <t>panel_close_2d</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>UI panel slides out</t>
+        </is>
+      </c>
+      <c r="C87" s="12" t="inlineStr">
+        <is>
+          <t>Platformer 2D</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>Panel swoops closed — sine falling slide from mid to low, mirrored close</t>
+        </is>
+      </c>
+      <c r="E87" s="12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F87" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I87" s="12" t="n">
+        <v>620</v>
+      </c>
+      <c r="J87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="12" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="L87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" s="12" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="T87" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="U87" s="12" t="inlineStr">
+        <is>
+          <t>sine</t>
+        </is>
+      </c>
+      <c r="V87" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="W87" s="12" t="n">
+        <v>22050</v>
+      </c>
+      <c r="X87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Z87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB87" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AC87" s="12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AD87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AF87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AI87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ87" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AK87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL87" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AM87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ87" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AR87" s="12" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="AS87" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AT87" s="5" t="inlineStr">
+        <is>
+          <t>New platformer preset: mirror of panel_open_2d — starts high, falls with negative slide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="12" t="inlineStr">
+        <is>
+          <t>collectable</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>Sparkly item collect</t>
+        </is>
+      </c>
+      <c r="C88" s="12" t="inlineStr">
+        <is>
+          <t>Platformer 2D</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>Bright gem/star/ring collect — very high square with fast arp and upward slide</t>
+        </is>
+      </c>
+      <c r="E88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G88" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="H88" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I88" s="12" t="n">
+        <v>1800</v>
+      </c>
+      <c r="J88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L88" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="M88" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" s="12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="Q88" s="12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R88" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="S88" s="12" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="T88" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="U88" s="12" t="inlineStr">
+        <is>
+          <t>square</t>
+        </is>
+      </c>
+      <c r="V88" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="W88" s="12" t="n">
+        <v>22050</v>
+      </c>
+      <c r="X88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Z88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB88" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AC88" s="12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AD88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AF88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AI88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ88" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AK88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL88" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AM88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ88" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AR88" s="12" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="AS88" s="12" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AT88" s="5" t="inlineStr">
+        <is>
+          <t>New platformer preset: sparkly gem/star collect. Higher freq than pickup (1800 vs 2200) with arp for multi-note shimmer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="12" t="inlineStr">
+        <is>
+          <t>clang</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>Hard metal impact</t>
+        </is>
+      </c>
+      <c r="C89" s="12" t="inlineStr">
+        <is>
+          <t>Platformer 2D</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>Sharp metal clang — sawtooth with instant punch, fast vibrato ring-out, HPF for brightness</t>
+        </is>
+      </c>
+      <c r="E89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G89" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="H89" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="I89" s="12" t="n">
+        <v>350</v>
+      </c>
+      <c r="J89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" s="12" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="L89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N89" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="O89" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="P89" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" s="12" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="T89" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="U89" s="12" t="inlineStr">
+        <is>
+          <t>sawtooth</t>
+        </is>
+      </c>
+      <c r="V89" s="12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="W89" s="12" t="n">
+        <v>6000</v>
+      </c>
+      <c r="X89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="Z89" s="12" t="n">
+        <v>180</v>
+      </c>
+      <c r="AA89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB89" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AC89" s="12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AD89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE89" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AF89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH89" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AI89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ89" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AK89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL89" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AM89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ89" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AR89" s="12" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="AS89" s="12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AT89" s="5" t="inlineStr">
+        <is>
+          <t>New platformer preset: hard metal clang for sword hits, metal gates, crates. Punch 90, fast vibrato decay gives ringing metallic character.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="12" t="inlineStr">
+        <is>
+          <t>wobble</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>Springy rubber bounce</t>
+        </is>
+      </c>
+      <c r="C90" s="12" t="inlineStr">
+        <is>
+          <t>Platformer 2D</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>Rubbery wobble — sine with heavy vibrato giving a cartoon spring/bounce feel</t>
+        </is>
+      </c>
+      <c r="E90" s="12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F90" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G90" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="H90" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I90" s="12" t="n">
+        <v>380</v>
+      </c>
+      <c r="J90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="L90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N90" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="O90" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="P90" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" s="12" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="T90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U90" s="12" t="inlineStr">
+        <is>
+          <t>sine</t>
+        </is>
+      </c>
+      <c r="V90" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="W90" s="12" t="n">
+        <v>22050</v>
+      </c>
+      <c r="X90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y90" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Z90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB90" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AC90" s="12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AD90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE90" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AF90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH90" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AI90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ90" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AK90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL90" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AM90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ90" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AR90" s="12" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="AS90" s="12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AT90" s="5" t="inlineStr">
+        <is>
+          <t>New platformer preset: rubbery wobble. Vibrato depth 60 at speed 18 creates the characteristic wobble. Positive slide adds cartoon stretch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="12" t="inlineStr">
+        <is>
+          <t>checkpoint</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>Reached a save point</t>
+        </is>
+      </c>
+      <c r="C91" s="12" t="inlineStr">
+        <is>
+          <t>Platformer 2D</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>Save point activated — 2-note ascending arp, satisfying but brief. More restrained than quest_complete</t>
+        </is>
+      </c>
+      <c r="E91" s="12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F91" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I91" s="12" t="n">
+        <v>660</v>
+      </c>
+      <c r="J91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L91" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M91" s="12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N91" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="O91" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="P91" s="12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="Q91" s="12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R91" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="S91" s="12" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="T91" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="U91" s="12" t="inlineStr">
+        <is>
+          <t>square</t>
+        </is>
+      </c>
+      <c r="V91" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="W91" s="12" t="n">
+        <v>22050</v>
+      </c>
+      <c r="X91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Z91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AC91" s="12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AD91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AF91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AI91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ91" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AK91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL91" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AM91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ91" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AR91" s="12" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="AS91" s="12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AT91" s="5" t="inlineStr">
+        <is>
+          <t>New platformer preset: checkpoint save point. Ascending 2-note arp, gentle vibrato. Shorter and less grand than quest_complete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="12" t="inlineStr">
+        <is>
+          <t>button_click_2d</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>Soft menu button tap</t>
+        </is>
+      </c>
+      <c r="C92" s="12" t="inlineStr">
+        <is>
+          <t>Platformer 2D</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>Soft UI button press — triangle wave for warmth, very short, slight downward slide</t>
+        </is>
+      </c>
+      <c r="E92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="12" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I92" s="12" t="n">
+        <v>900</v>
+      </c>
+      <c r="J92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" s="12" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="L92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" s="12" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="T92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U92" s="12" t="inlineStr">
+        <is>
+          <t>triangle</t>
+        </is>
+      </c>
+      <c r="V92" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="W92" s="12" t="n">
+        <v>22050</v>
+      </c>
+      <c r="X92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Z92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB92" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AC92" s="12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AD92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AF92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AI92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ92" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AK92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL92" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AM92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ92" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AR92" s="12" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="AS92" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AT92" s="5" t="inlineStr">
+        <is>
+          <t>New platformer preset: triangle wave gives warmer softer click vs square. Slight negative slide feels like a key depressing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="12" t="inlineStr">
+        <is>
+          <t>boing</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>Springboard launch</t>
+        </is>
+      </c>
+      <c r="C93" s="12" t="inlineStr">
+        <is>
+          <t>Platformer 2D</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>Classic cartoon boing — sine with extreme positive slide, high punch, instant attack</t>
+        </is>
+      </c>
+      <c r="E93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G93" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="H93" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I93" s="12" t="n">
+        <v>180</v>
+      </c>
+      <c r="J93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" s="12" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L93" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M93" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" s="12" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="T93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U93" s="12" t="inlineStr">
+        <is>
+          <t>sine</t>
+        </is>
+      </c>
+      <c r="V93" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="W93" s="12" t="n">
+        <v>22050</v>
+      </c>
+      <c r="X93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Z93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB93" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AC93" s="12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AD93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AF93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AI93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ93" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AK93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL93" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AM93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ93" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AR93" s="12" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="AS93" s="12" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AT93" s="5" t="inlineStr">
+        <is>
+          <t>New platformer preset: classic boing. Starts low (180 Hz), extreme slide 0.85 rockets pitch upward. Delta slide 0.1 accelerates the rise. Punch 60 for snap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="12" t="inlineStr">
+        <is>
+          <t>quest_complete</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>Objective cleared fanfare</t>
+        </is>
+      </c>
+      <c r="C94" s="12" t="inlineStr">
+        <is>
+          <t>Platformer 2D</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>Quest objective complete — longer triangle arp with vibrato and delta slide, more rewarding than checkpoint</t>
+        </is>
+      </c>
+      <c r="E94" s="12" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F94" s="12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I94" s="12" t="n">
+        <v>500</v>
+      </c>
+      <c r="J94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="L94" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="M94" s="12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N94" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="O94" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="P94" s="12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="Q94" s="12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R94" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="S94" s="12" t="inlineStr">
+        <is>
+          <t>updown</t>
+        </is>
+      </c>
+      <c r="T94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U94" s="12" t="inlineStr">
+        <is>
+          <t>triangle</t>
+        </is>
+      </c>
+      <c r="V94" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="W94" s="12" t="n">
+        <v>22050</v>
+      </c>
+      <c r="X94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Z94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AC94" s="12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AD94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AF94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AI94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ94" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AK94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL94" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AM94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ94" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AR94" s="12" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="AS94" s="12" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AT94" s="5" t="inlineStr">
+        <is>
+          <t>New platformer preset: quest/objective complete. Triangle for warmth, updown arp, vibrato shimmer, delta slide pushes it upward. Longer and warmer than checkpoint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="12" t="inlineStr">
+        <is>
+          <t>pickup_2d</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>Quick item grab</t>
+        </is>
+      </c>
+      <c r="C95" s="12" t="inlineStr">
+        <is>
+          <t>Platformer 2D</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>Instant item pickup — very high bright square, tiny positive slide, ultra short</t>
+        </is>
+      </c>
+      <c r="E95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G95" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="H95" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I95" s="12" t="n">
+        <v>2200</v>
+      </c>
+      <c r="J95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" s="12" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="T95" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="U95" s="12" t="inlineStr">
+        <is>
+          <t>square</t>
+        </is>
+      </c>
+      <c r="V95" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="W95" s="12" t="n">
+        <v>22050</v>
+      </c>
+      <c r="X95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y95" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Z95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB95" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AC95" s="12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AD95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE95" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AF95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH95" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AI95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ95" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AK95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL95" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AM95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ95" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AR95" s="12" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="AS95" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AT95" s="5" t="inlineStr">
+        <is>
+          <t>New platformer preset: basic pickup blip. Higher freq (2200 Hz) and shorter than collectable for generic health/ammo/small items.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="12" t="inlineStr">
+        <is>
+          <t>enter_portal</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>Pulled into portal</t>
+        </is>
+      </c>
+      <c r="C96" s="12" t="inlineStr">
+        <is>
+          <t>Platformer 2D</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>Entering a portal — sine descends with vibrato, LPF closes down, sucked-inward feel</t>
+        </is>
+      </c>
+      <c r="E96" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F96" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I96" s="12" t="n">
+        <v>880</v>
+      </c>
+      <c r="J96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" s="12" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="L96" s="12" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M96" s="12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N96" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="O96" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="P96" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" s="12" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="T96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U96" s="12" t="inlineStr">
+        <is>
+          <t>sine</t>
+        </is>
+      </c>
+      <c r="V96" s="12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="W96" s="12" t="n">
+        <v>3000</v>
+      </c>
+      <c r="X96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Z96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AC96" s="12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AD96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AF96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AI96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AK96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AM96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ96" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AR96" s="12" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="AS96" s="12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AT96" s="5" t="inlineStr">
+        <is>
+          <t>New platformer preset: portal entry. Sine descends steeply (-0.5 slide, -0.05 delta), LPF 3000 gives muffled inward-pull quality. Vibrato adds mystical shimmer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="12" t="inlineStr">
+        <is>
+          <t>exit_portal</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>Emerging from portal</t>
+        </is>
+      </c>
+      <c r="C97" s="12" t="inlineStr">
+        <is>
+          <t>Platformer 2D</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>Exiting a portal — sine rises with vibrato, expanding outward feel</t>
+        </is>
+      </c>
+      <c r="E97" s="12" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F97" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G97" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="H97" s="12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I97" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="J97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" s="12" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L97" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M97" s="12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N97" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="O97" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="P97" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" s="12" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="T97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U97" s="12" t="inlineStr">
+        <is>
+          <t>sine</t>
+        </is>
+      </c>
+      <c r="V97" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="W97" s="12" t="n">
+        <v>22050</v>
+      </c>
+      <c r="X97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Z97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB97" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AC97" s="12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AD97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AF97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AI97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ97" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AK97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL97" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AM97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ97" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AR97" s="12" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="AS97" s="12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AT97" s="5" t="inlineStr">
+        <is>
+          <t>New platformer preset: portal exit. Mirrors enter_portal — starts low (220 Hz), rises strongly (0.55 slide). Open LPF gives emerging/expanding feel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="12" t="inlineStr">
+        <is>
+          <t>footstep_2d</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>Generic platform step</t>
+        </is>
+      </c>
+      <c r="C98" s="12" t="inlineStr">
+        <is>
+          <t>Platformer 2D</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>Light platformer footstep — short noise burst, punchy, HPF for tap crispness</t>
+        </is>
+      </c>
+      <c r="E98" s="12" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="F98" s="12" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="G98" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="H98" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I98" s="12" t="n">
+        <v>400</v>
+      </c>
+      <c r="J98" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="K98" s="12" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="L98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" s="12" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="T98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U98" s="12" t="inlineStr">
+        <is>
+          <t>noise</t>
+        </is>
+      </c>
+      <c r="V98" s="12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="W98" s="12" t="n">
+        <v>7000</v>
+      </c>
+      <c r="X98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="Z98" s="12" t="n">
+        <v>250</v>
+      </c>
+      <c r="AA98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB98" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AC98" s="12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AD98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AF98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AI98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ98" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AK98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL98" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AM98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ98" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AR98" s="12" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="AS98" s="12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AT98" s="5" t="inlineStr">
+        <is>
+          <t>New platformer preset: generic light footstep. Short noise burst, HPF 250 Hz above fundamental for crispness. Lighter than step_stone, suitable for default surface.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="12" t="inlineStr">
+        <is>
+          <t>land_hard</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>Heavy landing impact</t>
+        </is>
+      </c>
+      <c r="C99" s="12" t="inlineStr">
+        <is>
+          <t>Platformer 2D</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>Player lands from a height — low punchy noise thud, instant, LPF keeps bass weight</t>
+        </is>
+      </c>
+      <c r="E99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G99" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="H99" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="I99" s="12" t="n">
+        <v>120</v>
+      </c>
+      <c r="J99" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K99" s="12" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="L99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" s="12" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="T99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U99" s="12" t="inlineStr">
+        <is>
+          <t>noise</t>
+        </is>
+      </c>
+      <c r="V99" s="12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="W99" s="12" t="n">
+        <v>2500</v>
+      </c>
+      <c r="X99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="Z99" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB99" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AC99" s="12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AD99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AF99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AI99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ99" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AK99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL99" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AM99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ99" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AR99" s="12" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="AS99" s="12" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AT99" s="5" t="inlineStr">
+        <is>
+          <t>New platformer preset: hard landing thud. Low freq (120 Hz), punch 80, LPF 2500 keeps weight. HPF 40 Hz just removes sub rumble. Heavier feel than any footstep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="12" t="inlineStr">
+        <is>
+          <t>hurt</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>Player takes damage</t>
+        </is>
+      </c>
+      <c r="C100" s="12" t="inlineStr">
+        <is>
+          <t>Platformer 2D</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>Damage hit — square descends steeply with vibrato buzz, classic game hurt sound</t>
+        </is>
+      </c>
+      <c r="E100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G100" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="H100" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="I100" s="12" t="n">
+        <v>340</v>
+      </c>
+      <c r="J100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" s="12" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="L100" s="12" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M100" s="12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N100" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="O100" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="P100" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" s="12" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="T100" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="U100" s="12" t="inlineStr">
+        <is>
+          <t>square</t>
+        </is>
+      </c>
+      <c r="V100" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="W100" s="12" t="n">
+        <v>22050</v>
+      </c>
+      <c r="X100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Z100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AC100" s="12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AD100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AF100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AI100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ100" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AK100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL100" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AM100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ100" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AR100" s="12" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="AS100" s="12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AT100" s="5" t="inlineStr">
+        <is>
+          <t>New platformer preset: classic damage sound. Strong descending slide (-0.7) with vibrato buzz. Delta slide -0.05 accelerates the fall.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="12" t="inlineStr">
+        <is>
+          <t>power_down</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>Power lost / death</t>
+        </is>
+      </c>
+      <c r="C101" s="12" t="inlineStr">
+        <is>
+          <t>Platformer 2D</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>Losing a life or power — sawtooth descends with accelerating pitch drop, longer and more dramatic</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F101" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="12" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I101" s="12" t="n">
+        <v>520</v>
+      </c>
+      <c r="J101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" s="12" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="L101" s="12" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="M101" s="12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N101" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="O101" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="P101" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" s="12" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="T101" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="U101" s="12" t="inlineStr">
+        <is>
+          <t>sawtooth</t>
+        </is>
+      </c>
+      <c r="V101" s="12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="W101" s="12" t="n">
+        <v>4000</v>
+      </c>
+      <c r="X101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Z101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AC101" s="12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AD101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AF101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AI101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ101" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AK101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL101" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AM101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ101" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AR101" s="12" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="AS101" s="12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AT101" s="5" t="inlineStr">
+        <is>
+          <t>New platformer preset: power/life lost. Delta slide -0.12 accelerates the pitch spiral down. Sawtooth with LPF gives a 'draining energy' quality. Longer than hurt for dramatic effect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="12" t="inlineStr">
+        <is>
+          <t>spring</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>Spring platform bounce</t>
+        </is>
+      </c>
+      <c r="C102" s="12" t="inlineStr">
+        <is>
+          <t>Platformer 2D</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>Spring platform — fast ascending arp with delta slide, punchy, distinct from boing</t>
+        </is>
+      </c>
+      <c r="E102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G102" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="H102" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I102" s="12" t="n">
+        <v>300</v>
+      </c>
+      <c r="J102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" s="12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L102" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M102" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" s="12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="Q102" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R102" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="S102" s="12" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="T102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U102" s="12" t="inlineStr">
+        <is>
+          <t>sine</t>
+        </is>
+      </c>
+      <c r="V102" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="W102" s="12" t="n">
+        <v>22050</v>
+      </c>
+      <c r="X102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Z102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AC102" s="12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AD102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AF102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AI102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AK102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL102" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AM102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ102" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AR102" s="12" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="AS102" s="12" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AT102" s="5" t="inlineStr">
+        <is>
+          <t>New platformer preset: spring platform. Unlike boing (single swoop), this uses fast arp 1.5x with delta slide 0.15 for a mechanical spring-release feel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="12" t="inlineStr">
+        <is>
+          <t>door_open</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>Wooden door swings open</t>
+        </is>
+      </c>
+      <c r="C103" s="12" t="inlineStr">
+        <is>
+          <t>Platformer 2D</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>Wooden door opening — low sawtooth creaks upward slowly, LPF keeps wood warmth</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F103" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I103" s="12" t="n">
+        <v>140</v>
+      </c>
+      <c r="J103" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="K103" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N103" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="O103" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="P103" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" s="12" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="T103" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="U103" s="12" t="inlineStr">
+        <is>
+          <t>sawtooth</t>
+        </is>
+      </c>
+      <c r="V103" s="12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="W103" s="12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="X103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y103" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Z103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB103" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AC103" s="12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AD103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE103" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AF103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH103" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AI103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ103" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AK103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL103" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AM103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ103" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AR103" s="12" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="AS103" s="12" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AT103" s="5" t="inlineStr">
+        <is>
+          <t>New platformer preset: wooden door opens. Low sawtooth 140 Hz with slight positive slide (door swinging). LPF 1000 Hz for woody warmth. Vibrato adds creak character.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="12" t="inlineStr">
+        <is>
+          <t>coin_drop</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>Coin tinks on ground</t>
+        </is>
+      </c>
+      <c r="C104" s="12" t="inlineStr">
+        <is>
+          <t>Platformer 2D</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>Coin hitting the floor — triangle with slight downward slide and punch, bright tink</t>
+        </is>
+      </c>
+      <c r="E104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G104" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="H104" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I104" s="12" t="n">
+        <v>1400</v>
+      </c>
+      <c r="J104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" s="12" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="L104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="N104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Q104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" s="12" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="T104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" s="12" t="inlineStr">
+        <is>
+          <t>triangle</t>
+        </is>
+      </c>
+      <c r="V104" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="W104" s="12" t="n">
+        <v>22050</v>
+      </c>
+      <c r="X104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y104" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Z104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB104" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AC104" s="12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AD104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE104" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AF104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH104" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AI104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ104" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AK104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL104" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AM104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ104" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="AR104" s="12" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="AS104" s="12" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AT104" s="5" t="inlineStr">
+        <is>
+          <t>New platformer preset: coin landing tink. Triangle for clean bright tone, punch 70 for immediate transient, slight negative slide for natural ringing decay.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:AT1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
